--- a/99. 부가업무/3. 6item 전력제어성 시험/csv/정리본/MVa FR_MVa RR_CVa_Su2i_QV_NX5e_전력제어성_제어표.xlsx
+++ b/99. 부가업무/3. 6item 전력제어성 시험/csv/정리본/MVa FR_MVa RR_CVa_Su2i_QV_NX5e_전력제어성_제어표.xlsx
@@ -9,21 +9,21 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11760" tabRatio="751"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11760" tabRatio="751" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="MVa_Front_0℃" sheetId="3" r:id="rId1"/>
-    <sheet name="MVa_Front_-30℃" sheetId="4" r:id="rId2"/>
-    <sheet name="MVa_Rear_0℃" sheetId="5" r:id="rId3"/>
-    <sheet name="MVa_Rear_-30℃" sheetId="6" r:id="rId4"/>
-    <sheet name="CVa_0C" sheetId="1" r:id="rId5"/>
-    <sheet name="CVa_-30℃" sheetId="2" r:id="rId6"/>
-    <sheet name="NX5e_0℃" sheetId="7" r:id="rId7"/>
-    <sheet name="NX5e_-30℃" sheetId="8" r:id="rId8"/>
-    <sheet name="QV_0℃" sheetId="9" r:id="rId9"/>
-    <sheet name="QV_-30℃" sheetId="10" r:id="rId10"/>
-    <sheet name="Su2i_0℃" sheetId="11" r:id="rId11"/>
-    <sheet name="Su2i_-30℃" sheetId="12" r:id="rId12"/>
+    <sheet name="MVa_Front_0℃_654V_300kgh" sheetId="3" r:id="rId1"/>
+    <sheet name="MVa_Front_-30℃_654V_300kgh" sheetId="4" r:id="rId2"/>
+    <sheet name="MVa_Rear_0℃_654V_300kgh" sheetId="5" r:id="rId3"/>
+    <sheet name="MVa_Rear_-30℃_654V_300kgh" sheetId="6" r:id="rId4"/>
+    <sheet name="CVa_0C_654V_300kgh" sheetId="1" r:id="rId5"/>
+    <sheet name="CVa_-30℃_654V_300kgh" sheetId="2" r:id="rId6"/>
+    <sheet name="NX5e_0℃_360V_300kgh" sheetId="7" r:id="rId7"/>
+    <sheet name="NX5e_-30℃_360V_300kgh" sheetId="8" r:id="rId8"/>
+    <sheet name="QV_0℃_358V_300kgh" sheetId="9" r:id="rId9"/>
+    <sheet name="QV_-30℃_358V_300kgh" sheetId="10" r:id="rId10"/>
+    <sheet name="Su2i_0℃_266V_300kgh" sheetId="11" r:id="rId11"/>
+    <sheet name="Su2i_-30℃_266V_300kgh" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -58,7 +58,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0&quot;W&quot;"/>
-    <numFmt numFmtId="178" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="177" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -653,7 +653,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -739,7 +739,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>MVa_Front_0℃!$B$1</c:f>
+              <c:f>MVa_Front_0℃_654V_300kgh!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -762,7 +762,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>MVa_Front_0℃!$A$2:$A$162</c:f>
+              <c:f>MVa_Front_0℃_654V_300kgh!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -1254,7 +1254,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>MVa_Front_0℃!$B$2:$B$162</c:f>
+              <c:f>MVa_Front_0℃_654V_300kgh!$B$2:$B$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -1756,7 +1756,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>MVa_Front_0℃!$C$1</c:f>
+              <c:f>MVa_Front_0℃_654V_300kgh!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1779,7 +1779,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>MVa_Front_0℃!$A$2:$A$162</c:f>
+              <c:f>MVa_Front_0℃_654V_300kgh!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -2271,7 +2271,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>MVa_Front_0℃!$C$2:$C$162</c:f>
+              <c:f>MVa_Front_0℃_654V_300kgh!$C$2:$C$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -2989,7 +2989,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'QV_-30℃'!$B$1</c:f>
+              <c:f>'QV_-30℃_358V_300kgh'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3012,7 +3012,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'QV_-30℃'!$A$2:$A$162</c:f>
+              <c:f>'QV_-30℃_358V_300kgh'!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -3504,7 +3504,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'QV_-30℃'!$B$2:$B$162</c:f>
+              <c:f>'QV_-30℃_358V_300kgh'!$B$2:$B$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -4006,7 +4006,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'QV_-30℃'!$C$1</c:f>
+              <c:f>'QV_-30℃_358V_300kgh'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4029,7 +4029,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'QV_-30℃'!$A$2:$A$162</c:f>
+              <c:f>'QV_-30℃_358V_300kgh'!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -4521,7 +4521,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'QV_-30℃'!$C$2:$C$162</c:f>
+              <c:f>'QV_-30℃_358V_300kgh'!$C$2:$C$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -5240,7 +5240,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Su2i_0℃!$B$1</c:f>
+              <c:f>Su2i_0℃_266V_300kgh!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5263,7 +5263,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Su2i_0℃!$A$2:$A$162</c:f>
+              <c:f>Su2i_0℃_266V_300kgh!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -5755,7 +5755,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Su2i_0℃!$B$2:$B$162</c:f>
+              <c:f>Su2i_0℃_266V_300kgh!$B$2:$B$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -6257,7 +6257,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Su2i_0℃!$C$1</c:f>
+              <c:f>Su2i_0℃_266V_300kgh!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6280,7 +6280,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Su2i_0℃!$A$2:$A$162</c:f>
+              <c:f>Su2i_0℃_266V_300kgh!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -6772,7 +6772,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Su2i_0℃!$C$2:$C$162</c:f>
+              <c:f>Su2i_0℃_266V_300kgh!$C$2:$C$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -7490,7 +7490,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Su2i_-30℃'!$B$1</c:f>
+              <c:f>'Su2i_-30℃_266V_300kgh'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7513,7 +7513,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Su2i_-30℃'!$A$2:$A$162</c:f>
+              <c:f>'Su2i_-30℃_266V_300kgh'!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -8005,7 +8005,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Su2i_-30℃'!$B$2:$B$162</c:f>
+              <c:f>'Su2i_-30℃_266V_300kgh'!$B$2:$B$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -8507,7 +8507,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Su2i_-30℃'!$C$1</c:f>
+              <c:f>'Su2i_-30℃_266V_300kgh'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8530,7 +8530,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Su2i_-30℃'!$A$2:$A$162</c:f>
+              <c:f>'Su2i_-30℃_266V_300kgh'!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -9022,7 +9022,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Su2i_-30℃'!$C$2:$C$162</c:f>
+              <c:f>'Su2i_-30℃_266V_300kgh'!$C$2:$C$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -9740,7 +9740,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'MVa_Front_-30℃'!$B$1</c:f>
+              <c:f>'MVa_Front_-30℃_654V_300kgh'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9763,7 +9763,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'MVa_Front_-30℃'!$A$2:$A$162</c:f>
+              <c:f>'MVa_Front_-30℃_654V_300kgh'!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -10255,7 +10255,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'MVa_Front_-30℃'!$B$2:$B$162</c:f>
+              <c:f>'MVa_Front_-30℃_654V_300kgh'!$B$2:$B$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -10757,7 +10757,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'MVa_Front_-30℃'!$C$1</c:f>
+              <c:f>'MVa_Front_-30℃_654V_300kgh'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10780,7 +10780,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'MVa_Front_-30℃'!$A$2:$A$162</c:f>
+              <c:f>'MVa_Front_-30℃_654V_300kgh'!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -11272,7 +11272,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'MVa_Front_-30℃'!$C$2:$C$162</c:f>
+              <c:f>'MVa_Front_-30℃_654V_300kgh'!$C$2:$C$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -11990,7 +11990,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>MVa_Rear_0℃!$B$1</c:f>
+              <c:f>MVa_Rear_0℃_654V_300kgh!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12013,7 +12013,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>MVa_Rear_0℃!$A$2:$A$162</c:f>
+              <c:f>MVa_Rear_0℃_654V_300kgh!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -12505,7 +12505,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>MVa_Rear_0℃!$B$2:$B$162</c:f>
+              <c:f>MVa_Rear_0℃_654V_300kgh!$B$2:$B$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -13007,7 +13007,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>MVa_Rear_0℃!$C$1</c:f>
+              <c:f>MVa_Rear_0℃_654V_300kgh!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13030,7 +13030,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>MVa_Rear_0℃!$A$2:$A$162</c:f>
+              <c:f>MVa_Rear_0℃_654V_300kgh!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -13522,7 +13522,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>MVa_Rear_0℃!$C$2:$C$162</c:f>
+              <c:f>MVa_Rear_0℃_654V_300kgh!$C$2:$C$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -14086,7 +14086,6 @@
         <c:axId val="985604863"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="2500"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -14241,7 +14240,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'MVa_Rear_-30℃'!$B$1</c:f>
+              <c:f>'MVa_Rear_-30℃_654V_300kgh'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14264,7 +14263,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'MVa_Rear_-30℃'!$A$2:$A$162</c:f>
+              <c:f>'MVa_Rear_-30℃_654V_300kgh'!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -14756,7 +14755,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'MVa_Rear_-30℃'!$B$2:$B$162</c:f>
+              <c:f>'MVa_Rear_-30℃_654V_300kgh'!$B$2:$B$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -15258,7 +15257,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'MVa_Rear_-30℃'!$C$1</c:f>
+              <c:f>'MVa_Rear_-30℃_654V_300kgh'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15281,7 +15280,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'MVa_Rear_-30℃'!$A$2:$A$162</c:f>
+              <c:f>'MVa_Rear_-30℃_654V_300kgh'!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -15773,7 +15772,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'MVa_Rear_-30℃'!$C$2:$C$162</c:f>
+              <c:f>'MVa_Rear_-30℃_654V_300kgh'!$C$2:$C$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -16491,7 +16490,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>CVa_0C!$B$1</c:f>
+              <c:f>CVa_0C_654V_300kgh!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -16514,7 +16513,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>CVa_0C!$A$2:$A$162</c:f>
+              <c:f>CVa_0C_654V_300kgh!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -17006,7 +17005,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>CVa_0C!$B$2:$B$162</c:f>
+              <c:f>CVa_0C_654V_300kgh!$B$2:$B$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -17508,7 +17507,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>CVa_0C!$C$1</c:f>
+              <c:f>CVa_0C_654V_300kgh!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -17531,7 +17530,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>CVa_0C!$A$2:$A$162</c:f>
+              <c:f>CVa_0C_654V_300kgh!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -18023,7 +18022,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>CVa_0C!$C$2:$C$162</c:f>
+              <c:f>CVa_0C_654V_300kgh!$C$2:$C$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -18557,7 +18556,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -18741,7 +18740,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'CVa_-30℃'!$B$1</c:f>
+              <c:f>'CVa_-30℃_654V_300kgh'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -18764,7 +18763,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'CVa_-30℃'!$A$2:$A$162</c:f>
+              <c:f>'CVa_-30℃_654V_300kgh'!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -19256,7 +19255,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'CVa_-30℃'!$B$2:$B$162</c:f>
+              <c:f>'CVa_-30℃_654V_300kgh'!$B$2:$B$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -19758,7 +19757,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'CVa_-30℃'!$C$1</c:f>
+              <c:f>'CVa_-30℃_654V_300kgh'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -19781,7 +19780,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'CVa_-30℃'!$A$2:$A$162</c:f>
+              <c:f>'CVa_-30℃_654V_300kgh'!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -20273,7 +20272,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'CVa_-30℃'!$C$2:$C$162</c:f>
+              <c:f>'CVa_-30℃_654V_300kgh'!$C$2:$C$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -20992,7 +20991,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>NX5e_0℃!$B$1</c:f>
+              <c:f>NX5e_0℃_360V_300kgh!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -21015,7 +21014,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>NX5e_0℃!$A$2:$A$162</c:f>
+              <c:f>NX5e_0℃_360V_300kgh!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -21507,7 +21506,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>NX5e_0℃!$B$2:$B$162</c:f>
+              <c:f>NX5e_0℃_360V_300kgh!$B$2:$B$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -22009,7 +22008,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>NX5e_0℃!$C$1</c:f>
+              <c:f>NX5e_0℃_360V_300kgh!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -22032,7 +22031,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>NX5e_0℃!$A$2:$A$162</c:f>
+              <c:f>NX5e_0℃_360V_300kgh!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -22524,7 +22523,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>NX5e_0℃!$C$2:$C$162</c:f>
+              <c:f>NX5e_0℃_360V_300kgh!$C$2:$C$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -23243,7 +23242,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'NX5e_-30℃'!$B$1</c:f>
+              <c:f>'NX5e_-30℃_360V_300kgh'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -23266,7 +23265,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'NX5e_-30℃'!$A$2:$A$162</c:f>
+              <c:f>'NX5e_-30℃_360V_300kgh'!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -23758,7 +23757,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'NX5e_-30℃'!$B$2:$B$162</c:f>
+              <c:f>'NX5e_-30℃_360V_300kgh'!$B$2:$B$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -24260,7 +24259,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'NX5e_-30℃'!$C$1</c:f>
+              <c:f>'NX5e_-30℃_360V_300kgh'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -24283,7 +24282,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'NX5e_-30℃'!$A$2:$A$162</c:f>
+              <c:f>'NX5e_-30℃_360V_300kgh'!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -24775,7 +24774,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'NX5e_-30℃'!$C$2:$C$162</c:f>
+              <c:f>'NX5e_-30℃_360V_300kgh'!$C$2:$C$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -25493,7 +25492,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>QV_0℃!$B$1</c:f>
+              <c:f>QV_0℃_358V_300kgh!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -25516,7 +25515,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>QV_0℃!$A$2:$A$162</c:f>
+              <c:f>QV_0℃_358V_300kgh!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -26008,7 +26007,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>QV_0℃!$B$2:$B$162</c:f>
+              <c:f>QV_0℃_358V_300kgh!$B$2:$B$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -26510,7 +26509,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>QV_0℃!$C$1</c:f>
+              <c:f>QV_0℃_358V_300kgh!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -26533,7 +26532,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>QV_0℃!$A$2:$A$162</c:f>
+              <c:f>QV_0℃_358V_300kgh!$A$2:$A$162</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="161"/>
@@ -27025,7 +27024,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>QV_0℃!$C$2:$C$162</c:f>
+              <c:f>QV_0℃_358V_300kgh!$C$2:$C$162</c:f>
               <c:numCache>
                 <c:formatCode>0"W"</c:formatCode>
                 <c:ptCount val="161"/>
